--- a/daily_matches/job_matches_2026-07-26.xlsx
+++ b/daily_matches/job_matches_2026-07-26.xlsx
@@ -468,227 +468,227 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Data Architect</t>
+          <t>Cloud Software Engineer - Egypt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Egypt, AR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.2</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, ChromaDB, S3, Glue, Redshift, Data Lake</t>
+          <t>S3, Glue, Athena, Redshift, Data Lake, Kinesis, FastAPI, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2cc185aab9474c</t>
+          <t>https://www.indeed.com/viewjob?jk=a89355d34c2e7d21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Appled AI Engineer</t>
+          <t>Senior Full-Stack &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VASERJOB</t>
+          <t>Inventive Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, S3, FastAPI, Kubernetes, Terraform, Git, PostgreSQL, Python</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Data Lake, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50a16cef0ea7b38</t>
+          <t>https://www.indeed.com/viewjob?jk=8dc578f11b30fa17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior QA Engineer - Egypt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Protagona</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Egypt, AR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Hadoop, Python, R</t>
+          <t>RAG, S3, Glue, Redshift, CI/CD, Jenkins, Git, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06a66005efe32de</t>
+          <t>https://www.indeed.com/viewjob?jk=fb073c25dabf3264</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer</t>
+          <t>AI Intern</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Recuro Health</t>
+          <t>Hendrickson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woodridge, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890a0cbf6effe0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=fad33537b51afafc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+          <t>Sr. Manufacturing Systems Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f66ac3cc90c2b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae5ecfeb0d7a920</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+          <t>Senior Full-Stack &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eef2bf3d8c3bbb7</t>
+          <t>https://www.indeed.com/viewjob?jk=1086056a31ef7d7d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+          <t>Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79bfbcc22c2d5e91</t>
+          <t>https://www.indeed.com/viewjob?jk=4a56d0b161524d45</t>
         </is>
       </c>
     </row>
